--- a/artfynd/A 26890-2022 artfynd.xlsx
+++ b/artfynd/A 26890-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26890-2022 artfynd.xlsx
+++ b/artfynd/A 26890-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>426289</v>
       </c>
       <c r="B2" t="n">
-        <v>99120</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516468.2394217322</v>
+        <v>516468</v>
       </c>
       <c r="R2" t="n">
-        <v>6578589.851790033</v>
+        <v>6578590</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,19 +757,9 @@
           <t>2006-05-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2006-05-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -821,15 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101947906</v>
+        <v>426291</v>
       </c>
       <c r="B3" t="n">
-        <v>99121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -854,24 +834,34 @@
           <t>Knaben</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mantorp, 600 m väst om, Nrk</t>
+          <t>Mantorp 600 m V, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516468.2438563348</v>
+        <v>516561</v>
       </c>
       <c r="R3" t="n">
-        <v>6578588.831744866</v>
+        <v>6578563</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,39 +885,39 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-05-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-05-24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Lokalen troligen återfunnen. Markbearbetat för ett antal år sedan. Glänta i skog.</t>
+          <t>Söder om vägen direkt inne i hagen, intill stor en. Yta 2 m2</t>
         </is>
       </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Kalkhällar och block i betesmark.</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Kalk</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -936,12 +926,527 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>Daniel Gustafson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram hällebräcka</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>56070260</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101947</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1449</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Hällebräcka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Saxifraga osloënsis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Knaben</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mantorp, 650 m V om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>516576</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6578565</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rinkaby</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>T-Öre-3855</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1999-12-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt – rikligt</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>markhällar i hage</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Örebro-Herbarium OREB</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Owe Nilsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lars Löfgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>94144941</v>
+      </c>
+      <c r="B5" t="n">
+        <v>108194</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mantorp, V om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>516507</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6578558</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rinkaby</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Arkiv-T-Öre-0117</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Endast plantor i knopp/blomning räknade. Svårt att bedöma antal sterila rosetter pga. bitvis hög övrig örtvegetation. Även 85 plantor ca 30 m öster om koordinat varav 10 norr om vägen.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Ohävdad ängsmark/gräsruderat.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>94144948</v>
+      </c>
+      <c r="B6" t="n">
+        <v>108194</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mantorp, V om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>516360</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6578578</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rinkaby</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Arkiv-T-Öre-0118</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Söder om vägen mot trädesåker.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Vägslänt, gräsbevuxen.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>94144982</v>
+      </c>
+      <c r="B7" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mantorp, V om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>516484</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6578564</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rinkaby</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Arkiv-T-Öre-0119</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>ängsmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 26890-2022 artfynd.xlsx
+++ b/artfynd/A 26890-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -803,6 +808,11 @@
           <t>Åtgärdsprogram hällebräcka</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/426289</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -934,6 +944,11 @@
           <t>Åtgärdsprogram hällebräcka</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/426291</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1055,6 +1070,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56070260</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1188,6 +1208,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94144941</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1321,6 +1346,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94144948</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1449,8 +1479,21 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94144982</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>